--- a/planilha.xlsx
+++ b/planilha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/paulo_cainelles_prestserv_petrobras_com_br/Documents/Área de Trabalho/nivelamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="14_{3AE44733-C139-4DCE-ACF7-7A76ECA3B1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61D79818-3A19-4F19-8460-24810ED385F4}"/>
+  <xr:revisionPtr revIDLastSave="422" documentId="14_{3AE44733-C139-4DCE-ACF7-7A76ECA3B1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13E17724-AE2F-41BB-8521-75ED21591C62}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="1000" xr2:uid="{6F1CD188-6D62-48EE-9C78-77398EC325CC}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="1000" xr2:uid="{6F1CD188-6D62-48EE-9C78-77398EC325CC}"/>
   </bookViews>
   <sheets>
     <sheet name="NIVELADAS" sheetId="4" r:id="rId1"/>
@@ -45,30 +45,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2701" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="291">
   <si>
     <t>SEMANA</t>
   </si>
@@ -1365,7 +1343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1453,37 +1431,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1538,6 +1488,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2666,10 +2645,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.55392215808882472</c:v>
+                  <c:v>0.35754296698326549</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39494147827481157</c:v>
+                  <c:v>0.84624491180461336</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4859,21 +4838,22 @@
     <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="47"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="64"/>
     </row>
     <row r="3" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="24" t="s">
@@ -4955,14 +4935,14 @@
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="2:30" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="47"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="64"/>
     </row>
     <row r="8" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="24" t="s">
@@ -5036,14 +5016,14 @@
       <c r="G11" s="23"/>
     </row>
     <row r="12" spans="2:30" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="64"/>
       <c r="AD12" t="s">
         <v>42</v>
       </c>
@@ -5117,39 +5097,39 @@
     </row>
     <row r="16" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="51" t="s">
+      <c r="C17" s="66"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="52"/>
-      <c r="G17" s="53"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="70"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="65"/>
-      <c r="I18" s="66" t="s">
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="55"/>
+      <c r="I18" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="67"/>
-      <c r="K18" s="68"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="58"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
       <c r="I19" s="34" t="s">
         <v>39</v>
       </c>
@@ -5163,12 +5143,12 @@
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="57"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="59"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
       <c r="I20" s="36" t="s">
         <v>37</v>
       </c>
@@ -5182,12 +5162,12 @@
       </c>
     </row>
     <row r="21" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="57"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="59"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
       <c r="I21" s="38" t="s">
         <v>38</v>
       </c>
@@ -5201,83 +5181,83 @@
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="57"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="59"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="57"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="59"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="57"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="59"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="57"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="59"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="49"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="57"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="59"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="57"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="59"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="69"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="71"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="61"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="64"/>
-      <c r="G29" s="65"/>
-      <c r="I29" s="66" t="s">
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="55"/>
+      <c r="I29" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="J29" s="67"/>
-      <c r="K29" s="68"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="58"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="54"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="56"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="46"/>
       <c r="I30" s="34" t="s">
         <v>39</v>
       </c>
@@ -5291,12 +5271,12 @@
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="57"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="59"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="49"/>
       <c r="I31" s="36" t="s">
         <v>37</v>
       </c>
@@ -5310,12 +5290,12 @@
       </c>
     </row>
     <row r="32" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="57"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="59"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="49"/>
       <c r="I32" s="38" t="s">
         <v>38</v>
       </c>
@@ -5329,89 +5309,89 @@
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B33" s="57"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="59"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="49"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="57"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="59"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="49"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="57"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="59"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="49"/>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="57"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="59"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="49"/>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="57"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="59"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="49"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="57"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="59"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="49"/>
     </row>
     <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="69"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="71"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="61"/>
     </row>
     <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="65"/>
-      <c r="I40" s="66" t="s">
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="55"/>
+      <c r="I40" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="J40" s="67"/>
-      <c r="K40" s="68"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="58"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B41" s="54"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="46"/>
       <c r="I41" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="41">
-        <f>E14</f>
-        <v>1.2037878787878789</v>
+      <c r="J41" s="71">
+        <f>SUM(J42:J43)</f>
+        <v>1340</v>
       </c>
       <c r="K41" s="35">
         <f>E14</f>
@@ -5419,12 +5399,12 @@
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="57"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="59"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="49"/>
       <c r="I42" s="36" t="s">
         <v>37</v>
       </c>
@@ -5432,18 +5412,18 @@
         <f>'MANDTU T.E'!H1</f>
         <v>398</v>
       </c>
-      <c r="K42" s="37" cm="1">
-        <f t="array" ref="K42:K43">K20:K21</f>
-        <v>0.55392215808882472</v>
+      <c r="K42" s="72">
+        <f>K41*J42/J41</f>
+        <v>0.35754296698326549</v>
       </c>
     </row>
     <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="57"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="59"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="49"/>
       <c r="I43" s="38" t="s">
         <v>38</v>
       </c>
@@ -5452,132 +5432,135 @@
         <v>942</v>
       </c>
       <c r="K43" s="40">
-        <v>0.39494147827481157</v>
+        <f>K41*J43/J41</f>
+        <v>0.84624491180461336</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="57"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="59"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="49"/>
       <c r="N44">
         <v>100</v>
       </c>
-      <c r="O44" s="42">
+      <c r="O44" s="41">
         <f>SUM(J47+J48)</f>
-        <v>1.1356875634653412</v>
+        <v>1.2206623109400887</v>
       </c>
     </row>
     <row r="45" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="57"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="59"/>
-      <c r="N45" t="s">
-        <v>24</v>
-      </c>
-      <c r="O45" s="43">
+      <c r="B45" s="47"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="49"/>
+      <c r="O45" s="42">
         <f>J47*N44</f>
-        <v>58.787756954185177</v>
+        <v>52.241783917333208</v>
       </c>
     </row>
     <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="57"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="59"/>
-      <c r="I46" s="66" t="s">
+      <c r="B46" s="47"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="49"/>
+      <c r="I46" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J46" s="67"/>
-      <c r="K46" s="68"/>
-      <c r="O46" s="43">
+      <c r="J46" s="57"/>
+      <c r="K46" s="58"/>
+      <c r="O46" s="42">
         <f>J48*N44</f>
-        <v>54.780999392348939</v>
+        <v>69.824447176675662</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="57"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="59"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="49"/>
       <c r="I47" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="42">
+      <c r="J47" s="41">
         <f>SUM(K19+K31+K42)/3</f>
-        <v>0.58787756954185177</v>
+        <v>0.52241783917333207</v>
       </c>
       <c r="K47" s="1">
         <f>K51</f>
-        <v>0.51764022822267397</v>
+        <v>0.42797900327650312</v>
       </c>
     </row>
     <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="57"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="59"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="49"/>
       <c r="I48" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="J48" s="42">
+      <c r="J48" s="41">
         <f>SUM(K21+K32+K43)/3</f>
-        <v>0.54780999392348939</v>
+        <v>0.69824447176675664</v>
       </c>
     </row>
     <row r="49" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="57"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="59"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="49"/>
     </row>
     <row r="50" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="60"/>
-      <c r="C50" s="61"/>
-      <c r="D50" s="61"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="62"/>
-      <c r="I50" s="66" t="s">
+      <c r="B50" s="50"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="52"/>
+      <c r="I50" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="J50" s="67"/>
-      <c r="K50" s="68"/>
-      <c r="N50" s="42"/>
+      <c r="J50" s="57"/>
+      <c r="K50" s="58"/>
+      <c r="N50" s="41"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I51" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="K51" s="44">
+      <c r="K51" s="43">
         <f>O45/O44/100</f>
-        <v>0.51764022822267397</v>
+        <v>0.42797900327650312</v>
       </c>
     </row>
     <row r="52" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I52" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="K52" s="44">
+      <c r="K52" s="43">
         <f>O46/O44/100</f>
-        <v>0.48235977177732603</v>
+        <v>0.57202099672349693</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:G17"/>
     <mergeCell ref="B41:G50"/>
     <mergeCell ref="B40:G40"/>
     <mergeCell ref="I46:K46"/>
@@ -5589,11 +5572,6 @@
     <mergeCell ref="B19:G28"/>
     <mergeCell ref="B30:G39"/>
     <mergeCell ref="I50:K50"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
   </mergeCells>
   <conditionalFormatting sqref="F51:F1048576 F1:F16">
     <cfRule type="colorScale" priority="1">

--- a/planilha.xlsx
+++ b/planilha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://petrobrasbr-my.sharepoint.com/personal/paulo_cainelles_prestserv_petrobras_com_br/Documents/Área de Trabalho/nivelamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="422" documentId="14_{3AE44733-C139-4DCE-ACF7-7A76ECA3B1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13E17724-AE2F-41BB-8521-75ED21591C62}"/>
+  <xr:revisionPtr revIDLastSave="463" documentId="14_{3AE44733-C139-4DCE-ACF7-7A76ECA3B1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{960772FA-4F17-4D05-B545-18D402DB6507}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="1000" xr2:uid="{6F1CD188-6D62-48EE-9C78-77398EC325CC}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="291">
   <si>
     <t>SEMANA</t>
   </si>
@@ -783,9 +783,6 @@
     <t>VE-40035 M.A. p/ passagem de cabo</t>
   </si>
   <si>
-    <t>B-40142B-M.A bancada acesso vaso acumula</t>
-  </si>
-  <si>
     <t>B-40142C-M.A. barraca/escora de linha</t>
   </si>
   <si>
@@ -919,6 +916,9 @@
   </si>
   <si>
     <t>B-7454: Montar andaime de acesso</t>
+  </si>
+  <si>
+    <t>B-40142C-M.A bancada acesso vaso acumula</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1434,6 +1434,33 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1488,35 +1515,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4846,14 +4844,14 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="64"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
     </row>
     <row r="3" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="24" t="s">
@@ -4935,14 +4933,14 @@
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="2:30" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="64"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46"/>
     </row>
     <row r="8" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="24" t="s">
@@ -5016,14 +5014,14 @@
       <c r="G11" s="23"/>
     </row>
     <row r="12" spans="2:30" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="64"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="46"/>
       <c r="AD12" t="s">
         <v>42</v>
       </c>
@@ -5097,39 +5095,39 @@
     </row>
     <row r="16" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="65" t="s">
+      <c r="B17" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="66"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="68" t="s">
+      <c r="C17" s="48"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="69"/>
-      <c r="G17" s="70"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="52"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="55"/>
-      <c r="I18" s="56" t="s">
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="64"/>
+      <c r="I18" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="57"/>
-      <c r="K18" s="58"/>
+      <c r="J18" s="66"/>
+      <c r="K18" s="67"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="44"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="55"/>
       <c r="I19" s="34" t="s">
         <v>39</v>
       </c>
@@ -5143,12 +5141,12 @@
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="47"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="58"/>
       <c r="I20" s="36" t="s">
         <v>37</v>
       </c>
@@ -5162,12 +5160,12 @@
       </c>
     </row>
     <row r="21" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="58"/>
       <c r="I21" s="38" t="s">
         <v>38</v>
       </c>
@@ -5181,83 +5179,83 @@
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="47"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="47"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="47"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="49"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="58"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="47"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="58"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="47"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="49"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="49"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="58"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="59"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="61"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="70"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="55"/>
-      <c r="I29" s="56" t="s">
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="64"/>
+      <c r="I29" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="J29" s="57"/>
-      <c r="K29" s="58"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="67"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="44"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="55"/>
       <c r="I30" s="34" t="s">
         <v>39</v>
       </c>
@@ -5271,12 +5269,12 @@
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="47"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="49"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="58"/>
       <c r="I31" s="36" t="s">
         <v>37</v>
       </c>
@@ -5290,12 +5288,12 @@
       </c>
     </row>
     <row r="32" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="47"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="58"/>
       <c r="I32" s="38" t="s">
         <v>38</v>
       </c>
@@ -5309,87 +5307,87 @@
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B33" s="47"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="49"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="58"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="47"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="58"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="47"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="49"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="58"/>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="47"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="58"/>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="47"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="49"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="58"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="47"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="49"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="58"/>
     </row>
     <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="59"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="61"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="70"/>
     </row>
     <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="55"/>
-      <c r="I40" s="56" t="s">
+      <c r="C40" s="63"/>
+      <c r="D40" s="63"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="64"/>
+      <c r="I40" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="J40" s="57"/>
-      <c r="K40" s="58"/>
+      <c r="J40" s="66"/>
+      <c r="K40" s="67"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B41" s="44"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="46"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="55"/>
       <c r="I41" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="71">
+      <c r="J41" s="33">
         <f>SUM(J42:J43)</f>
         <v>1340</v>
       </c>
@@ -5399,12 +5397,12 @@
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="47"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="49"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="58"/>
       <c r="I42" s="36" t="s">
         <v>37</v>
       </c>
@@ -5412,18 +5410,18 @@
         <f>'MANDTU T.E'!H1</f>
         <v>398</v>
       </c>
-      <c r="K42" s="72">
+      <c r="K42" s="37">
         <f>K41*J42/J41</f>
         <v>0.35754296698326549</v>
       </c>
     </row>
     <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="47"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="49"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="58"/>
       <c r="I43" s="38" t="s">
         <v>38</v>
       </c>
@@ -5437,12 +5435,12 @@
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="47"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="49"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="58"/>
       <c r="N44">
         <v>100</v>
       </c>
@@ -5452,41 +5450,41 @@
       </c>
     </row>
     <row r="45" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="47"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="58"/>
       <c r="O45" s="42">
         <f>J47*N44</f>
         <v>52.241783917333208</v>
       </c>
     </row>
     <row r="46" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="47"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="49"/>
-      <c r="I46" s="56" t="s">
+      <c r="B46" s="56"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="58"/>
+      <c r="I46" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="J46" s="57"/>
-      <c r="K46" s="58"/>
+      <c r="J46" s="66"/>
+      <c r="K46" s="67"/>
       <c r="O46" s="42">
         <f>J48*N44</f>
         <v>69.824447176675662</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="47"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="49"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="58"/>
       <c r="I47" s="36" t="s">
         <v>37</v>
       </c>
@@ -5500,12 +5498,12 @@
       </c>
     </row>
     <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="47"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="49"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="58"/>
       <c r="I48" s="38" t="s">
         <v>38</v>
       </c>
@@ -5515,25 +5513,25 @@
       </c>
     </row>
     <row r="49" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="47"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="49"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="58"/>
     </row>
     <row r="50" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="50"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="52"/>
-      <c r="I50" s="56" t="s">
+      <c r="B50" s="59"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="60"/>
+      <c r="E50" s="60"/>
+      <c r="F50" s="60"/>
+      <c r="G50" s="61"/>
+      <c r="I50" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="J50" s="57"/>
-      <c r="K50" s="58"/>
+      <c r="J50" s="66"/>
+      <c r="K50" s="67"/>
       <c r="N50" s="41"/>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.25">
@@ -5556,11 +5554,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
     <mergeCell ref="B41:G50"/>
     <mergeCell ref="B40:G40"/>
     <mergeCell ref="I46:K46"/>
@@ -5572,6 +5565,11 @@
     <mergeCell ref="B19:G28"/>
     <mergeCell ref="B30:G39"/>
     <mergeCell ref="I50:K50"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:G17"/>
   </mergeCells>
   <conditionalFormatting sqref="F51:F1048576 F1:F16">
     <cfRule type="colorScale" priority="1">
@@ -7626,7 +7624,7 @@
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -11273,7 +11271,7 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="G12">
         <v>4</v>
@@ -11344,7 +11342,7 @@
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G13">
         <v>4</v>
@@ -11415,7 +11413,7 @@
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G14">
         <v>4</v>
@@ -11486,7 +11484,7 @@
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G15">
         <v>4</v>
@@ -11557,7 +11555,7 @@
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G16">
         <v>4</v>
@@ -11628,7 +11626,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G17">
         <v>4</v>
@@ -11699,7 +11697,7 @@
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -11729,7 +11727,7 @@
         <v>19</v>
       </c>
       <c r="P18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q18" t="s">
         <v>13</v>
@@ -11770,7 +11768,7 @@
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -11912,7 +11910,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -11983,7 +11981,7 @@
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G22">
         <v>4</v>
@@ -12054,7 +12052,7 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G23">
         <v>4</v>
@@ -12125,7 +12123,7 @@
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -12196,7 +12194,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G25">
         <v>4</v>
@@ -12267,7 +12265,7 @@
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -12338,7 +12336,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G27">
         <v>4</v>
@@ -12406,7 +12404,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G28">
         <v>4</v>
@@ -12474,7 +12472,7 @@
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -12542,7 +12540,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G30">
         <v>4</v>
@@ -21744,7 +21742,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G27">
         <v>4</v>
@@ -21809,7 +21807,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G28">
         <v>4</v>
@@ -21874,7 +21872,7 @@
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -21939,7 +21937,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G30">
         <v>4</v>
@@ -22004,7 +22002,7 @@
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -22075,7 +22073,7 @@
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G32">
         <v>4</v>
@@ -22146,7 +22144,7 @@
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G33">
         <v>4</v>
@@ -22214,7 +22212,7 @@
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G34">
         <v>4</v>
@@ -22288,7 +22286,7 @@
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -22359,7 +22357,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -22430,7 +22428,7 @@
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -22495,7 +22493,7 @@
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -22560,7 +22558,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G39">
         <v>4</v>
@@ -22631,7 +22629,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -22702,7 +22700,7 @@
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -22773,7 +22771,7 @@
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -22844,7 +22842,7 @@
         <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -22915,7 +22913,7 @@
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -22986,7 +22984,7 @@
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -23054,7 +23052,7 @@
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -23152,7 +23150,7 @@
         <v>0.59250000000000003</v>
       </c>
       <c r="O47" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P47" t="s">
         <v>14</v>
@@ -23193,7 +23191,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G48">
         <v>4</v>
@@ -23264,7 +23262,7 @@
         <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -23335,7 +23333,7 @@
         <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -23406,7 +23404,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G51">
         <v>4</v>
@@ -23477,7 +23475,7 @@
         <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G52">
         <v>4</v>
@@ -23545,7 +23543,7 @@
         <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G53">
         <v>4</v>
@@ -23612,10 +23610,10 @@
   <sheetPr filterMode="1">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:AF106"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>113</v>
       </c>
@@ -23703,17 +23701,8 @@
       <c r="AC1" t="s">
         <v>113</v>
       </c>
-      <c r="AD1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>112410188</v>
       </c>
@@ -23781,7 +23770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>107181770</v>
       </c>
@@ -23849,7 +23838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>112410189</v>
       </c>
@@ -23917,7 +23906,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>105945436</v>
       </c>
@@ -23988,7 +23977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>133844745</v>
       </c>
@@ -24059,7 +24048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>133844756</v>
       </c>
@@ -24130,7 +24119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>114052334</v>
       </c>
@@ -24198,7 +24187,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>134596247</v>
       </c>
@@ -24266,7 +24255,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>116655735</v>
       </c>
@@ -24337,7 +24326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>117101929</v>
       </c>
@@ -24408,7 +24397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>132993858</v>
       </c>
@@ -24479,7 +24468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>119630572</v>
       </c>
@@ -24547,7 +24536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>119630574</v>
       </c>
@@ -24615,7 +24604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>125733769</v>
       </c>
@@ -24686,7 +24675,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>121381330</v>
       </c>
@@ -26028,7 +26017,7 @@
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="G35">
         <v>4</v>
@@ -26099,7 +26088,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -26170,7 +26159,7 @@
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G37">
         <v>4</v>
@@ -26241,7 +26230,7 @@
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -26312,7 +26301,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G39">
         <v>4</v>
@@ -26377,7 +26366,7 @@
         <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -26442,7 +26431,7 @@
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G41">
         <v>4</v>
@@ -26507,7 +26496,7 @@
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -26572,7 +26561,7 @@
         <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -26643,7 +26632,7 @@
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -26714,7 +26703,7 @@
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -26785,7 +26774,7 @@
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -26853,7 +26842,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -26924,7 +26913,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G48">
         <v>4</v>
@@ -26998,7 +26987,7 @@
         <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -27069,7 +27058,7 @@
         <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -27140,7 +27129,7 @@
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G51">
         <v>4</v>
@@ -27205,7 +27194,7 @@
         <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G52">
         <v>4</v>
@@ -27270,7 +27259,7 @@
         <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G53">
         <v>4</v>
@@ -27300,7 +27289,7 @@
         <v>19</v>
       </c>
       <c r="P53" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q53" t="s">
         <v>13</v>
@@ -27341,7 +27330,7 @@
         <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -27412,7 +27401,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G55">
         <v>4</v>
@@ -27483,7 +27472,7 @@
         <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G56">
         <v>4</v>
@@ -27554,7 +27543,7 @@
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G57">
         <v>4</v>
@@ -27625,7 +27614,7 @@
         <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G58">
         <v>4</v>
@@ -27696,7 +27685,7 @@
         <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G59">
         <v>4</v>
@@ -27767,7 +27756,7 @@
         <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G60">
         <v>4</v>
@@ -27909,7 +27898,7 @@
         <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G62">
         <v>4</v>
@@ -27980,7 +27969,7 @@
         <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G63">
         <v>4</v>
@@ -28051,7 +28040,7 @@
         <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G64">
         <v>4</v>
@@ -28119,7 +28108,7 @@
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G65">
         <v>4</v>
@@ -28217,7 +28206,7 @@
         <v>0.59250000000000003</v>
       </c>
       <c r="O66" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P66" t="s">
         <v>14</v>
@@ -28258,7 +28247,7 @@
         <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G67">
         <v>4</v>
@@ -28329,7 +28318,7 @@
         <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G68">
         <v>4</v>
@@ -28400,7 +28389,7 @@
         <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G69">
         <v>4</v>
@@ -28471,7 +28460,7 @@
         <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G70">
         <v>4</v>
@@ -28542,7 +28531,7 @@
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G71">
         <v>4</v>
@@ -28613,7 +28602,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G72">
         <v>4</v>
@@ -28684,7 +28673,7 @@
         <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G73">
         <v>4</v>
@@ -28755,7 +28744,7 @@
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G74">
         <v>4</v>
@@ -28826,7 +28815,7 @@
         <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -28894,7 +28883,7 @@
         <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G76">
         <v>4</v>
@@ -28962,7 +28951,7 @@
         <v>10</v>
       </c>
       <c r="F77" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G77">
         <v>4</v>
@@ -29030,7 +29019,7 @@
         <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G78">
         <v>4</v>
@@ -29098,7 +29087,7 @@
         <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G79">
         <v>4</v>
@@ -29166,7 +29155,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G80">
         <v>4</v>
@@ -29220,157 +29209,157 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L81" s="18"/>
       <c r="N81" s="18"/>
       <c r="T81" s="18"/>
       <c r="W81" s="18"/>
     </row>
-    <row r="82" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L82" s="18"/>
       <c r="N82" s="18"/>
       <c r="T82" s="18"/>
       <c r="W82" s="18"/>
     </row>
-    <row r="83" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L83" s="18"/>
       <c r="N83" s="18"/>
       <c r="T83" s="18"/>
       <c r="W83" s="18"/>
     </row>
-    <row r="84" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L84" s="18"/>
       <c r="N84" s="18"/>
       <c r="T84" s="18"/>
       <c r="W84" s="18"/>
     </row>
-    <row r="85" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L85" s="18"/>
       <c r="N85" s="18"/>
       <c r="T85" s="18"/>
       <c r="W85" s="18"/>
     </row>
-    <row r="86" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L86" s="18"/>
       <c r="N86" s="18"/>
       <c r="T86" s="18"/>
       <c r="W86" s="18"/>
     </row>
-    <row r="87" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L87" s="18"/>
       <c r="N87" s="18"/>
       <c r="T87" s="18"/>
       <c r="W87" s="18"/>
     </row>
-    <row r="88" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L88" s="18"/>
       <c r="N88" s="18"/>
       <c r="T88" s="18"/>
       <c r="W88" s="18"/>
     </row>
-    <row r="89" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L89" s="18"/>
       <c r="N89" s="18"/>
       <c r="T89" s="18"/>
       <c r="W89" s="18"/>
     </row>
-    <row r="90" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L90" s="18"/>
       <c r="N90" s="18"/>
       <c r="T90" s="18"/>
       <c r="W90" s="18"/>
     </row>
-    <row r="91" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L91" s="18"/>
       <c r="N91" s="18"/>
       <c r="T91" s="18"/>
       <c r="W91" s="18"/>
     </row>
-    <row r="92" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L92" s="18"/>
       <c r="N92" s="18"/>
       <c r="T92" s="18"/>
       <c r="W92" s="18"/>
     </row>
-    <row r="93" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L93" s="18"/>
       <c r="N93" s="18"/>
       <c r="T93" s="18"/>
       <c r="W93" s="18"/>
     </row>
-    <row r="94" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L94" s="18"/>
       <c r="N94" s="18"/>
       <c r="T94" s="18"/>
       <c r="W94" s="18"/>
     </row>
-    <row r="95" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L95" s="18"/>
       <c r="N95" s="18"/>
       <c r="T95" s="18"/>
       <c r="W95" s="18"/>
     </row>
-    <row r="96" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L96" s="18"/>
       <c r="N96" s="18"/>
       <c r="T96" s="18"/>
       <c r="W96" s="18"/>
     </row>
-    <row r="97" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L97" s="18"/>
       <c r="N97" s="18"/>
       <c r="T97" s="18"/>
       <c r="W97" s="18"/>
     </row>
-    <row r="98" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L98" s="18"/>
       <c r="N98" s="18"/>
       <c r="T98" s="18"/>
       <c r="W98" s="18"/>
     </row>
-    <row r="99" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L99" s="18"/>
       <c r="N99" s="18"/>
       <c r="T99" s="18"/>
       <c r="W99" s="18"/>
     </row>
-    <row r="100" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L100" s="18"/>
       <c r="N100" s="18"/>
       <c r="T100" s="18"/>
       <c r="W100" s="18"/>
     </row>
-    <row r="101" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L101" s="18"/>
       <c r="N101" s="18"/>
       <c r="T101" s="18"/>
       <c r="W101" s="18"/>
     </row>
-    <row r="102" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L102" s="18"/>
       <c r="N102" s="18"/>
       <c r="T102" s="18"/>
       <c r="W102" s="19"/>
     </row>
-    <row r="103" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L103" s="18"/>
       <c r="N103" s="18"/>
       <c r="T103" s="18"/>
       <c r="W103" s="19"/>
     </row>
-    <row r="104" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L104" s="18"/>
       <c r="N104" s="18"/>
       <c r="T104" s="18"/>
       <c r="W104" s="18"/>
     </row>
-    <row r="105" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L105" s="18"/>
       <c r="N105" s="18"/>
       <c r="T105" s="18"/>
       <c r="W105" s="19"/>
     </row>
-    <row r="106" spans="12:23" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="12:23" x14ac:dyDescent="0.25">
       <c r="L106" s="18"/>
       <c r="N106" s="18"/>
       <c r="T106" s="18"/>
@@ -29379,7 +29368,7 @@
   </sheetData>
   <autoFilter ref="A1:AF106" xr:uid="{2BCEC47D-41DE-4BB3-AD6B-E0546668367F}">
     <filterColumn colId="28">
-      <filters>
+      <filters blank="1">
         <filter val="19"/>
       </filters>
     </filterColumn>
